--- a/Analisis_Rotaciones_Potrero_Actual.xlsx
+++ b/Analisis_Rotaciones_Potrero_Actual.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,50 +465,55 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Altura promedio de ingreso (cm)</t>
+          <t>Altura promedio actual (cm)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Altura promedio anterior (cm)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Mediciones válidas</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Medición 1 (Altura del Pasto)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Medición 2 (Altura del Pasto)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Medición 3 (Altura del Pasto)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Medición 4 (Altura del Pasto)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Medición 5 (Altura del Pasto)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Medición 6 (Altura del Pasto)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Medición 7 (Altura del Pasto)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -543,12 +548,10 @@
         <v>36.42857142857143</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>32.85714285714285</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -557,7 +560,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -567,20 +570,25 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>30 cm</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>40 cm</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Muchas maleza (chaparro)</t>
         </is>
@@ -615,12 +623,10 @@
         <v>31.42857142857143</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30 cm</t>
-        </is>
+        <v>37.14285714285715</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -644,7 +650,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -653,6 +659,11 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>35 cm</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">Buen estado </t>
         </is>
@@ -687,12 +698,10 @@
         <v>32.14285714285715</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30 cm</t>
-        </is>
+        <v>32.85714285714285</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -711,7 +720,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -724,7 +733,12 @@
           <t>35 cm</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>35 cm</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -755,12 +769,10 @@
         <v>37.85714285714285</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
+        <v>38.57142857142857</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -769,30 +781,35 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>35 cm</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">Buen estado </t>
         </is>
@@ -827,12 +844,10 @@
         <v>36.42857142857143</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>35.71428571428572</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -846,7 +861,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -861,10 +876,15 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>30 cm</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t xml:space="preserve">Buen estado </t>
         </is>
@@ -899,12 +919,10 @@
         <v>37.85714285714285</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>36.42857142857143</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -918,7 +936,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -937,6 +955,11 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cuadro con 40%bajo poco pasto </t>
         </is>
@@ -970,19 +993,15 @@
       <c r="G8" t="n">
         <v>42.85714285714285</v>
       </c>
-      <c r="H8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>40 cm</t>
@@ -990,25 +1009,30 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Primer ingreso potrero con muchas maleza (chaparro guayacana y escobilla)</t>
         </is>
@@ -1043,12 +1067,10 @@
         <v>37.14285714285715</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>37.14285714285715</v>
+      </c>
+      <c r="I9" t="n">
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1057,7 +1079,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1067,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1077,10 +1099,15 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t xml:space="preserve">Cuadro con 40%bajo poco pasto mucha maleza chaparro rastrojo </t>
         </is>
@@ -1115,31 +1142,29 @@
         <v>39.28571428571428</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
+        <v>41.42857142857143</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1149,10 +1174,15 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>35 cm</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t xml:space="preserve">Buen estado </t>
         </is>
@@ -1187,16 +1217,14 @@
         <v>33.57142857142857</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1211,7 +1239,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1221,10 +1249,15 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Potrero con una 70% maleza (chaparro rastrojo)</t>
         </is>
@@ -1259,21 +1292,19 @@
         <v>34.28571428571428</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>42.14285714285715</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1288,15 +1319,20 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t xml:space="preserve">Buen estado </t>
         </is>
@@ -1331,12 +1367,10 @@
         <v>36.42857142857143</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>37.85714285714285</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1345,17 +1379,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1369,6 +1403,11 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t xml:space="preserve">Buen estado </t>
         </is>
@@ -1402,19 +1441,15 @@
       <c r="G14" t="n">
         <v>40</v>
       </c>
-      <c r="H14" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>40 cm</t>
@@ -1422,25 +1457,30 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>35 cm</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t xml:space="preserve">Buen estado </t>
         </is>
@@ -1475,23 +1515,21 @@
         <v>40</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" t="inlineStr">
+        <v>35</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>40 cm</t>
@@ -1509,10 +1547,15 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
+        <is>
+          <t>30 cm</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t xml:space="preserve">Potrero 90% bajo </t>
         </is>
@@ -1547,12 +1590,10 @@
         <v>38.57142857142857</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
+        <v>39.28571428571428</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1561,7 +1602,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1571,20 +1612,25 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>35 cm</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t xml:space="preserve">Buen estado </t>
         </is>
@@ -1619,23 +1665,21 @@
         <v>42.85714285714285</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>40 cm</t>
@@ -1648,15 +1692,20 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t xml:space="preserve">Primer ingreso </t>
         </is>
@@ -1691,18 +1740,16 @@
         <v>40.71428571428572</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>40 cm</t>
@@ -1710,25 +1757,30 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>35 cm</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
+        <is>
+          <t>35 cm</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t xml:space="preserve">Potrero con mucha maleza ( chaparro rastrojo guayacana) </t>
         </is>
@@ -1763,36 +1815,34 @@
         <v>37.14285714285715</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
+        <v>38.57142857142857</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1801,6 +1851,11 @@
         </is>
       </c>
       <c r="P19" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t xml:space="preserve">Cuadro con 40%bajo poco pasto </t>
         </is>
@@ -1835,12 +1890,10 @@
         <v>37.85714285714285</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>37.85714285714285</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1849,7 +1902,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1859,12 +1912,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1873,6 +1926,11 @@
         </is>
       </c>
       <c r="P20" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Potrero con bastante rastrojo chaparro un 40%</t>
         </is>
@@ -1907,31 +1965,29 @@
         <v>32.14285714285715</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30 cm</t>
-        </is>
+        <v>31.42857142857143</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1941,10 +1997,15 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
+        <is>
+          <t>35 cm</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t xml:space="preserve">Potrero con 30 % bajo </t>
         </is>
@@ -1979,36 +2040,34 @@
         <v>37.14285714285715</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
+        <v>36.42857142857143</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>30 cm</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2017,6 +2076,11 @@
         </is>
       </c>
       <c r="P22" t="inlineStr">
+        <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t xml:space="preserve">Potrero con mucha maleza ( chaparro rastrojo) </t>
         </is>
@@ -2051,23 +2115,21 @@
         <v>39.28571428571428</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" t="inlineStr">
+        <v>36.42857142857143</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>40 cm</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>40 cm</t>
@@ -2080,15 +2142,20 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>35 cm</t>
+          <t>40 cm</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>30 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
+        <is>
+          <t>30 cm</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t xml:space="preserve">Rotación con el acceso crítico pradera en buen estado </t>
         </is>
@@ -2123,12 +2190,10 @@
         <v>39.28571428571428</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>35 cm</t>
-        </is>
+        <v>39.28571428571428</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2137,7 +2202,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>40 cm</t>
+          <t>35 cm</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2157,10 +2222,15 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>40 cm</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>45 cm</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Potrero con mucha maleza (chaparro escobilla y espina )</t>
         </is>
